--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487623_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487623_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0086</v>
+        <v>4.0847</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5965</v>
+        <v>5.9178</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5879</v>
+        <v>-1.8332</v>
       </c>
       <c r="G2" t="n">
         <v>6.4121</v>
@@ -610,13 +610,13 @@
         <v>0.7761</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1646</v>
+        <v>-0.0886</v>
       </c>
       <c r="T2" t="n">
-        <v>0.268</v>
+        <v>0.5894</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4327</v>
+        <v>-0.678</v>
       </c>
       <c r="V2" t="n">
         <v>1.8358</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9894</v>
+        <v>3.6223</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7612</v>
+        <v>3.4214</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2281</v>
+        <v>0.2009</v>
       </c>
       <c r="G3" t="n">
         <v>1.6171</v>
@@ -688,13 +688,13 @@
         <v>0.3881</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4305</v>
+        <v>0.0634</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5462</v>
+        <v>0.2064</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1157</v>
+        <v>-0.143</v>
       </c>
       <c r="V3" t="n">
         <v>1.5537</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3652</v>
+        <v>2.3835</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5275</v>
+        <v>3.6276</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1623</v>
+        <v>-1.2441</v>
       </c>
       <c r="G4" t="n">
         <v>2.8571</v>
@@ -766,13 +766,13 @@
         <v>0.3881</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.88</v>
+        <v>-0.8616</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1211</v>
+        <v>-0.021</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7588</v>
+        <v>-0.8406</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. GOMA</t>
+          <t>J. VAQUERO PASCUAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2093</v>
+        <v>1.8577</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5155</v>
+        <v>2.6318</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6938</v>
+        <v>-0.7741</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0436</v>
+        <v>-1.2855</v>
       </c>
       <c r="H5" t="n">
-        <v>2.086</v>
+        <v>1.941</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9576</v>
+        <v>-3.2265</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1726</v>
+        <v>1.7155</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0103</v>
+        <v>3.7074</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1624</v>
+        <v>-1.9919</v>
       </c>
       <c r="M5" t="n">
-        <v>0.871</v>
+        <v>-3.001</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07580000000000001</v>
+        <v>-1.7664</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7952</v>
+        <v>-1.2346</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.3284</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9105</v>
+        <v>-1.9403</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5821</v>
+        <v>1.9403</v>
       </c>
       <c r="S5" t="n">
-        <v>1.212</v>
+        <v>1.6372</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3593</v>
+        <v>1.3506</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1473</v>
+        <v>0.2866</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2821</v>
+        <v>1.506</v>
       </c>
       <c r="W5" t="n">
-        <v>0.894</v>
+        <v>1.506</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. VERDERA BENASSAR</t>
+          <t>G. GOMA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8028999999999999</v>
+        <v>1.7754</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3754</v>
+        <v>1.1361</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4275</v>
+        <v>0.6393</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.0275</v>
+        <v>3.0436</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.0704</v>
+        <v>2.086</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9571</v>
+        <v>0.9576</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.6124</v>
+        <v>2.1726</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3996</v>
+        <v>2.0103</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2129</v>
+        <v>0.1624</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.415</v>
+        <v>0.871</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.6708</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2558</v>
+        <v>0.7952</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7761</v>
+        <v>-2.3284</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7463</v>
+        <v>0.5821</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6065</v>
+        <v>0.7781</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5103</v>
+        <v>0.98</v>
       </c>
       <c r="U6" t="n">
-        <v>0.09619999999999999</v>
+        <v>-0.2019</v>
       </c>
       <c r="V6" t="n">
-        <v>2.4477</v>
+        <v>0.2821</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4477</v>
+        <v>0.894</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. VAQUERO PASCUAL</t>
+          <t>T. VERDERA BENASSAR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.299</v>
+        <v>1.2728</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2093</v>
+        <v>0.7363</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9104</v>
+        <v>0.5365</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2855</v>
+        <v>-3.0275</v>
       </c>
       <c r="H7" t="n">
-        <v>1.941</v>
+        <v>-2.0704</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.2265</v>
+        <v>-0.9571</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7155</v>
+        <v>-1.6124</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7074</v>
+        <v>-0.3996</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.9919</v>
+        <v>-1.2129</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.001</v>
+        <v>-1.415</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7664</v>
+        <v>-1.6708</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2346</v>
+        <v>0.2558</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.7761</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9403</v>
+        <v>1.7463</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0785</v>
+        <v>1.0764</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0718</v>
+        <v>0.8712</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1503</v>
+        <v>0.2053</v>
       </c>
       <c r="V7" t="n">
-        <v>1.506</v>
+        <v>2.4477</v>
       </c>
       <c r="W7" t="n">
-        <v>1.506</v>
+        <v>2.4477</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1597</v>
+        <v>0.7695</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8947000000000001</v>
+        <v>1.7771</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.735</v>
+        <v>-1.0075</v>
       </c>
       <c r="G8" t="n">
         <v>1.9421</v>
@@ -1078,13 +1078,13 @@
         <v>1.3582</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9937</v>
+        <v>1.6036</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2804</v>
+        <v>1.1628</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7134</v>
+        <v>0.4408</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2239</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1249</v>
+        <v>0.2067</v>
       </c>
       <c r="E9" t="n">
         <v>2.6774</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5525</v>
+        <v>-2.4707</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7029</v>
@@ -1156,13 +1156,13 @@
         <v>0.9702</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1397</v>
+        <v>0.2215</v>
       </c>
       <c r="T9" t="n">
         <v>0.6191</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4794</v>
+        <v>-0.3976</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2821</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1165</v>
+        <v>-0.0014</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7473</v>
+        <v>-0.6867</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6308</v>
+        <v>0.6853</v>
       </c>
       <c r="G10" t="n">
         <v>0.0412</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1577</v>
+        <v>-0.0426</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1211</v>
+        <v>-0.0606</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0366</v>
+        <v>0.0179</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4635</v>
+        <v>-1.7611</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7071</v>
+        <v>0.3277</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1706</v>
+        <v>-2.0888</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8518</v>
@@ -1312,13 +1312,13 @@
         <v>1.9403</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7465000000000001</v>
+        <v>0.4489</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4333</v>
+        <v>1.054</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6868</v>
+        <v>-0.6051</v>
       </c>
       <c r="V11" t="n">
         <v>0.6119</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5703</v>
+        <v>-2.5069</v>
       </c>
       <c r="E12" t="n">
-        <v>1.1049</v>
+        <v>1.0048</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.6752</v>
+        <v>-3.5117</v>
       </c>
       <c r="G12" t="n">
         <v>-0.4669</v>
@@ -1390,13 +1390,13 @@
         <v>1.3582</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9094</v>
+        <v>-0.8459</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2557</v>
+        <v>0.1556</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1651</v>
+        <v>-1.0015</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6119</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.2007</v>
+        <v>-5.1868</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.9855</v>
+        <v>-3.0261</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2152</v>
+        <v>-2.1607</v>
       </c>
       <c r="G13" t="n">
         <v>-3.2718</v>
@@ -1468,13 +1468,13 @@
         <v>1.1642</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3905</v>
+        <v>1.4045</v>
       </c>
       <c r="T13" t="n">
-        <v>2.27</v>
+        <v>1.2295</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1205</v>
+        <v>0.175</v>
       </c>
       <c r="V13" t="n">
         <v>-2.5433</v>
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.608000000000001</v>
+        <v>6.516399999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>18.6367</v>
+        <v>19.5452</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.0289</v>
+        <v>-13.0288</v>
       </c>
       <c r="G14" t="n">
         <v>5.3068</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5520000000000003</v>
+        <v>0.5520000000000012</v>
       </c>
       <c r="I14" t="n">
-        <v>4.754799999999999</v>
+        <v>4.7548</v>
       </c>
       <c r="J14" t="n">
         <v>20.6282</v>
@@ -1537,7 +1537,7 @@
         <v>-2.1969</v>
       </c>
       <c r="P14" t="n">
-        <v>-7.761299999999999</v>
+        <v>-7.7613</v>
       </c>
       <c r="Q14" t="n">
         <v>-20.3734</v>
@@ -1546,13 +1546,13 @@
         <v>12.6121</v>
       </c>
       <c r="S14" t="n">
-        <v>4.4862</v>
+        <v>5.3949</v>
       </c>
       <c r="T14" t="n">
-        <v>7.228300000000001</v>
+        <v>8.137</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.742</v>
+        <v>-2.7421</v>
       </c>
       <c r="V14" t="n">
         <v>3.576</v>
@@ -1561,7 +1561,7 @@
         <v>11.1537</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.577500000000001</v>
+        <v>-7.577500000000002</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6528</v>
+        <v>3.1856</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4884</v>
+        <v>2.4874</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1644</v>
+        <v>0.6982</v>
       </c>
       <c r="G15" t="n">
         <v>1.6169</v>
@@ -1624,13 +1624,13 @@
         <v>1.3582</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9881</v>
+        <v>0.521</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6386</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3495</v>
+        <v>-0.1166</v>
       </c>
       <c r="V15" t="n">
         <v>0.6597</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. VIERA LOPEZ</t>
+          <t>J. ABRIL RAMIRO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0919</v>
+        <v>2.2227</v>
       </c>
       <c r="E16" t="n">
-        <v>5.7954</v>
+        <v>4.352</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.7035</v>
+        <v>-2.1293</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2711</v>
+        <v>-0.0271</v>
       </c>
       <c r="H16" t="n">
-        <v>1.815</v>
+        <v>2.2813</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-2.3084</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4538</v>
+        <v>3.1743</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2914</v>
+        <v>5.0545</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1624</v>
+        <v>-1.8802</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1827</v>
+        <v>-3.2014</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4764</v>
+        <v>-2.7732</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7063</v>
+        <v>-0.4282</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7463</v>
+        <v>2.7164</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>2.7164</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7671</v>
+        <v>-0.8816000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>3.6417</v>
+        <v>0.5658</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8746</v>
+        <v>-1.4474</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.6925</v>
+        <v>0.4149</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3299</v>
+        <v>0.6119</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.3627</v>
+        <v>-0.197</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ABRIL RAMIRO</t>
+          <t>D. VIERA LOPEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6193</v>
+        <v>1.1534</v>
       </c>
       <c r="E17" t="n">
-        <v>4.1518</v>
+        <v>3.293</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.5325</v>
+        <v>-2.1396</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0271</v>
+        <v>1.2711</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2813</v>
+        <v>1.815</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.3084</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1743</v>
+        <v>3.4538</v>
       </c>
       <c r="K17" t="n">
-        <v>5.0545</v>
+        <v>3.2914</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.8802</v>
+        <v>0.1624</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.2014</v>
+        <v>-2.1827</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.7732</v>
+        <v>-1.4764</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4282</v>
+        <v>-0.7063</v>
       </c>
       <c r="P17" t="n">
-        <v>2.7164</v>
+        <v>1.7463</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R17" t="n">
         <v>2.7164</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.485</v>
+        <v>0.8285</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3656</v>
+        <v>1.1392</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.8506</v>
+        <v>-0.3107</v>
       </c>
       <c r="V17" t="n">
-        <v>0.4149</v>
+        <v>-2.6925</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6119</v>
+        <v>-0.3299</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.197</v>
+        <v>-2.3627</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GASE SECO</t>
+          <t>K. SKUTYELNIK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3275</v>
+        <v>0.9002</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0606</v>
+        <v>-0.2349</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3881</v>
+        <v>1.135</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1335</v>
+        <v>-4.6384</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-2.1676</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1335</v>
+        <v>-2.4708</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-2.9896</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-1.0916</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-1.898</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1335</v>
+        <v>-1.6488</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-1.076</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1335</v>
+        <v>-0.5729</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3881</v>
+        <v>1.9403</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3881</v>
+        <v>2.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.194</v>
+        <v>-0.6853</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0606</v>
+        <v>-0.2288</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1335</v>
+        <v>-0.4564</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.2836</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.9537</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.125</v>
+        <v>0.7679</v>
       </c>
       <c r="E19" t="n">
-        <v>2.7525</v>
+        <v>3.1529</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.6275</v>
+        <v>-2.385</v>
       </c>
       <c r="G19" t="n">
         <v>2.0391</v>
@@ -1936,13 +1936,13 @@
         <v>1.9403</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4067</v>
+        <v>-0.7638</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5451</v>
+        <v>-0.1447</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8616</v>
+        <v>-0.6191</v>
       </c>
       <c r="V19" t="n">
         <v>-2.4477</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. SKUTYELNIK</t>
+          <t>A. GASE SECO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5736</v>
+        <v>0.3275</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0357</v>
+        <v>-0.0606</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4621</v>
+        <v>0.3881</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.6384</v>
+        <v>0.1335</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.1676</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.4708</v>
+        <v>0.1335</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.9896</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.0916</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.898</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6488</v>
+        <v>0.1335</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.076</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5729</v>
+        <v>0.1335</v>
       </c>
       <c r="P20" t="n">
-        <v>1.9403</v>
+        <v>0.3881</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.9105</v>
+        <v>0.3881</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.159</v>
+        <v>-0.194</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0296</v>
+        <v>-0.0606</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1294</v>
+        <v>-0.1335</v>
       </c>
       <c r="V20" t="n">
-        <v>4.2836</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>3.9537</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. LLACER SIMLAT</t>
+          <t>O. BALSELLS PLAZA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6697</v>
+        <v>-2.0549</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0837</v>
+        <v>0.2847</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.586</v>
+        <v>-2.3396</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.559</v>
+        <v>-0.678</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.6473</v>
+        <v>1.9847</v>
       </c>
       <c r="I21" t="n">
-        <v>2.0882</v>
+        <v>-2.6627</v>
       </c>
       <c r="J21" t="n">
-        <v>1.4304</v>
+        <v>2.0765</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.7589</v>
+        <v>2.6982</v>
       </c>
       <c r="L21" t="n">
-        <v>3.1894</v>
+        <v>-0.6217</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.9895</v>
+        <v>-2.7545</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.8883</v>
+        <v>-0.7135</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1011</v>
+        <v>-2.041</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3582</v>
+        <v>-3.1045</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9403</v>
+        <v>-3.8806</v>
       </c>
       <c r="R21" t="n">
-        <v>3.2985</v>
+        <v>0.7761</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0002</v>
+        <v>1.3978</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4262</v>
+        <v>0.865</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.4264</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4686</v>
+        <v>0.3299</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4686</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. BALSELLS PLAZA</t>
+          <t>E. LLACER SIMLAT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6888</v>
+        <v>-2.242</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2158</v>
+        <v>-0.0837</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4731</v>
+        <v>-2.1583</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.678</v>
+        <v>-1.559</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9847</v>
+        <v>-3.6473</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.6627</v>
+        <v>2.0882</v>
       </c>
       <c r="J22" t="n">
-        <v>2.0765</v>
+        <v>1.4304</v>
       </c>
       <c r="K22" t="n">
-        <v>2.6982</v>
+        <v>-1.7589</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6217</v>
+        <v>3.1894</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.7545</v>
+        <v>-2.9895</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7135</v>
+        <v>-1.8883</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.041</v>
+        <v>-1.1011</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.1045</v>
+        <v>1.3582</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.8806</v>
+        <v>-1.9403</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7761</v>
+        <v>3.2985</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7638</v>
+        <v>-0.5726</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3645</v>
+        <v>0.4262</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3993</v>
+        <v>-0.9987</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3299</v>
+        <v>-1.4686</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.894</v>
+        <v>-1.4686</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1795</v>
+        <v>-3.515</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6722</v>
+        <v>-0.2718</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.5073</v>
+        <v>-3.2432</v>
       </c>
       <c r="G23" t="n">
         <v>0.6881</v>
@@ -2248,13 +2248,13 @@
         <v>2.1344</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.9347</v>
+        <v>-1.2702</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0296</v>
+        <v>-0.6292</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9051</v>
+        <v>-0.641</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1866</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.3128</v>
+        <v>-3.6839</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0914</v>
+        <v>0.1098</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.2214</v>
+        <v>-3.7937</v>
       </c>
       <c r="G24" t="n">
         <v>-4.1528</v>
@@ -2326,13 +2326,13 @@
         <v>2.1344</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.8257</v>
+        <v>-0.1968</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0296</v>
+        <v>0.1716</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7961</v>
+        <v>-0.3684</v>
       </c>
       <c r="V24" t="n">
         <v>-1.4686</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.607900000000001</v>
+        <v>-2.938499999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>13.0287</v>
+        <v>13.0288</v>
       </c>
       <c r="F25" t="n">
-        <v>-18.6367</v>
+        <v>-15.9674</v>
       </c>
       <c r="G25" t="n">
         <v>-5.3066</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.5520000000000009</v>
+        <v>-0.552</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.7547</v>
+        <v>-4.754700000000001</v>
       </c>
       <c r="J25" t="n">
         <v>15.3214</v>
@@ -2383,7 +2383,7 @@
         <v>13.1245</v>
       </c>
       <c r="L25" t="n">
-        <v>2.196899999999999</v>
+        <v>2.1969</v>
       </c>
       <c r="M25" t="n">
         <v>-20.6282</v>
@@ -2404,13 +2404,13 @@
         <v>20.3733</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.4863</v>
+        <v>-1.817</v>
       </c>
       <c r="T25" t="n">
         <v>2.7421</v>
       </c>
       <c r="U25" t="n">
-        <v>-7.2285</v>
+        <v>-4.559</v>
       </c>
       <c r="V25" t="n">
         <v>-3.5759</v>
